--- a/Impact modelling/Runs_water_municipalities_months.xlsx
+++ b/Impact modelling/Runs_water_municipalities_months.xlsx
@@ -479,7 +479,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -494,21 +494,21 @@
         <v>14</v>
       </c>
       <c r="H3">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
       </c>
       <c r="K3">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -523,21 +523,21 @@
         <v>14</v>
       </c>
       <c r="H4">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
       </c>
       <c r="K4">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -551,22 +551,16 @@
       <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="H5">
-        <v>0.52</v>
-      </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
       </c>
-      <c r="K5">
-        <v>0.52</v>
-      </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -581,21 +575,21 @@
         <v>14</v>
       </c>
       <c r="H6">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
       </c>
       <c r="K6">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -610,21 +604,21 @@
         <v>14</v>
       </c>
       <c r="H7">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J7" t="s">
         <v>15</v>
       </c>
       <c r="K7">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -647,7 +641,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -662,10 +656,10 @@
         <v>14</v>
       </c>
       <c r="H9">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J9" t="s">
         <v>15</v>
@@ -676,7 +670,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -699,7 +693,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -713,22 +707,16 @@
       <c r="G11" t="s">
         <v>14</v>
       </c>
-      <c r="H11">
-        <v>0.5</v>
-      </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
       </c>
-      <c r="K11">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -746,7 +734,7 @@
         <v>0.5</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
@@ -757,7 +745,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -772,10 +760,10 @@
         <v>14</v>
       </c>
       <c r="H13">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J13" t="s">
         <v>15</v>
@@ -786,7 +774,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -809,7 +797,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -824,21 +812,21 @@
         <v>14</v>
       </c>
       <c r="H15">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="I15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J15" t="s">
         <v>15</v>
       </c>
       <c r="K15">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -853,21 +841,21 @@
         <v>14</v>
       </c>
       <c r="H16">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="I16">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J16" t="s">
         <v>15</v>
       </c>
       <c r="K16">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -882,10 +870,10 @@
         <v>14</v>
       </c>
       <c r="H17">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J17" t="s">
         <v>15</v>
@@ -896,7 +884,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
@@ -914,7 +902,7 @@
         <v>0.48</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
@@ -925,7 +913,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
@@ -940,21 +928,21 @@
         <v>14</v>
       </c>
       <c r="H19">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J19" t="s">
         <v>15</v>
       </c>
       <c r="K19">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
@@ -969,10 +957,10 @@
         <v>14</v>
       </c>
       <c r="H20">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="I20">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J20" t="s">
         <v>15</v>
@@ -983,7 +971,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
@@ -1001,7 +989,7 @@
         <v>0.5</v>
       </c>
       <c r="I21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J21" t="s">
         <v>15</v>
@@ -1012,7 +1000,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
@@ -1027,21 +1015,21 @@
         <v>14</v>
       </c>
       <c r="H22">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="I22">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
       </c>
       <c r="K22">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
@@ -1056,21 +1044,21 @@
         <v>14</v>
       </c>
       <c r="H23">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="I23">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="J23" t="s">
         <v>15</v>
       </c>
       <c r="K23">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
@@ -1093,7 +1081,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
@@ -1108,21 +1096,21 @@
         <v>14</v>
       </c>
       <c r="H25">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="I25">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="J25" t="s">
         <v>15</v>
       </c>
       <c r="K25">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
@@ -1137,21 +1125,21 @@
         <v>14</v>
       </c>
       <c r="H26">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I26">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="J26" t="s">
         <v>15</v>
       </c>
       <c r="K26">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
@@ -1169,7 +1157,7 @@
         <v>0.44</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="s">
         <v>15</v>
@@ -1180,7 +1168,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
@@ -1198,7 +1186,7 @@
         <v>0.55</v>
       </c>
       <c r="I28">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
@@ -1209,7 +1197,7 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="1">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
@@ -1224,21 +1212,21 @@
         <v>14</v>
       </c>
       <c r="H29">
+        <v>0.6</v>
+      </c>
+      <c r="I29">
+        <v>111</v>
+      </c>
+      <c r="J29" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29">
         <v>0.59</v>
-      </c>
-      <c r="I29">
-        <v>63</v>
-      </c>
-      <c r="J29" t="s">
-        <v>15</v>
-      </c>
-      <c r="K29">
-        <v>0.58</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
@@ -1256,7 +1244,7 @@
         <v>0.46</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
@@ -1267,7 +1255,7 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
@@ -1282,21 +1270,21 @@
         <v>14</v>
       </c>
       <c r="H31">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="I31">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
       </c>
       <c r="K31">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
@@ -1314,7 +1302,7 @@
         <v>0.63</v>
       </c>
       <c r="I32">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="J32" t="s">
         <v>15</v>
@@ -1325,7 +1313,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="1">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
@@ -1343,7 +1331,7 @@
         <v>0.57</v>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J33" t="s">
         <v>15</v>
@@ -1354,7 +1342,7 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="1">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
@@ -1369,21 +1357,21 @@
         <v>14</v>
       </c>
       <c r="H34">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I34">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="J34" t="s">
         <v>15</v>
       </c>
       <c r="K34">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -1401,7 +1389,7 @@
         <v>0.62</v>
       </c>
       <c r="I35">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="J35" t="s">
         <v>15</v>
@@ -1412,7 +1400,7 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="1">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
@@ -1430,7 +1418,7 @@
         <v>0.49</v>
       </c>
       <c r="I36">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J36" t="s">
         <v>15</v>
@@ -1441,7 +1429,7 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="1">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
@@ -1459,13 +1447,13 @@
         <v>0.55</v>
       </c>
       <c r="I37">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="J37" t="s">
         <v>15</v>
       </c>
       <c r="K37">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Impact modelling/Runs_water_municipalities_months.xlsx
+++ b/Impact modelling/Runs_water_municipalities_months.xlsx
@@ -470,11 +470,17 @@
       <c r="G2" t="s">
         <v>14</v>
       </c>
+      <c r="H2">
+        <v>0.17</v>
+      </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
+      </c>
+      <c r="K2">
+        <v>0.17</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -494,16 +500,16 @@
         <v>14</v>
       </c>
       <c r="H3">
-        <v>0.55</v>
+        <v>0.22</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
       </c>
       <c r="K3">
-        <v>0.55</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -523,16 +529,16 @@
         <v>14</v>
       </c>
       <c r="H4">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
       </c>
       <c r="K4">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -551,11 +557,17 @@
       <c r="G5" t="s">
         <v>14</v>
       </c>
+      <c r="H5">
+        <v>0.25</v>
+      </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
+      </c>
+      <c r="K5">
+        <v>0.23</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -575,16 +587,16 @@
         <v>14</v>
       </c>
       <c r="H6">
-        <v>0.46</v>
+        <v>0.14</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
       </c>
       <c r="K6">
-        <v>0.45</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -604,16 +616,16 @@
         <v>14</v>
       </c>
       <c r="H7">
-        <v>0.59</v>
+        <v>0.31</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J7" t="s">
         <v>15</v>
       </c>
       <c r="K7">
-        <v>0.54</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -632,11 +644,17 @@
       <c r="G8" t="s">
         <v>14</v>
       </c>
+      <c r="H8">
+        <v>0.18</v>
+      </c>
       <c r="I8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="s">
         <v>15</v>
+      </c>
+      <c r="K8">
+        <v>0.17</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -656,16 +674,16 @@
         <v>14</v>
       </c>
       <c r="H9">
-        <v>0.51</v>
+        <v>0.27</v>
       </c>
       <c r="I9">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J9" t="s">
         <v>15</v>
       </c>
       <c r="K9">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -684,11 +702,17 @@
       <c r="G10" t="s">
         <v>14</v>
       </c>
+      <c r="H10">
+        <v>0.22</v>
+      </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="s">
         <v>15</v>
+      </c>
+      <c r="K10">
+        <v>0.22</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -708,7 +732,7 @@
         <v>14</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
@@ -731,16 +755,16 @@
         <v>14</v>
       </c>
       <c r="H12">
-        <v>0.5</v>
+        <v>0.03</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
       </c>
       <c r="K12">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -760,16 +784,16 @@
         <v>14</v>
       </c>
       <c r="H13">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="I13">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J13" t="s">
         <v>15</v>
       </c>
       <c r="K13">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -812,16 +836,16 @@
         <v>14</v>
       </c>
       <c r="H15">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="I15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J15" t="s">
         <v>15</v>
       </c>
       <c r="K15">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -841,16 +865,16 @@
         <v>14</v>
       </c>
       <c r="H16">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="I16">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J16" t="s">
         <v>15</v>
       </c>
       <c r="K16">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -870,16 +894,16 @@
         <v>14</v>
       </c>
       <c r="H17">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J17" t="s">
         <v>15</v>
       </c>
       <c r="K17">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -899,16 +923,16 @@
         <v>14</v>
       </c>
       <c r="H18">
-        <v>0.48</v>
+        <v>0.19</v>
       </c>
       <c r="I18">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
       </c>
       <c r="K18">
-        <v>0.48</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -928,16 +952,16 @@
         <v>14</v>
       </c>
       <c r="H19">
-        <v>0.48</v>
+        <v>0.27</v>
       </c>
       <c r="I19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J19" t="s">
         <v>15</v>
       </c>
       <c r="K19">
-        <v>0.48</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -957,16 +981,16 @@
         <v>14</v>
       </c>
       <c r="H20">
-        <v>0.55</v>
+        <v>0.29</v>
       </c>
       <c r="I20">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J20" t="s">
         <v>15</v>
       </c>
       <c r="K20">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -986,16 +1010,16 @@
         <v>14</v>
       </c>
       <c r="H21">
-        <v>0.5</v>
+        <v>0.16</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J21" t="s">
         <v>15</v>
       </c>
       <c r="K21">
-        <v>0.5</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1015,16 +1039,16 @@
         <v>14</v>
       </c>
       <c r="H22">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="I22">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
       </c>
       <c r="K22">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1044,16 +1068,16 @@
         <v>14</v>
       </c>
       <c r="H23">
-        <v>0.54</v>
+        <v>0.33</v>
       </c>
       <c r="I23">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="J23" t="s">
         <v>15</v>
       </c>
       <c r="K23">
-        <v>0.54</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1072,11 +1096,17 @@
       <c r="G24" t="s">
         <v>14</v>
       </c>
+      <c r="H24">
+        <v>0.21</v>
+      </c>
       <c r="I24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J24" t="s">
         <v>15</v>
+      </c>
+      <c r="K24">
+        <v>0.23</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1096,16 +1126,16 @@
         <v>14</v>
       </c>
       <c r="H25">
-        <v>0.53</v>
+        <v>0.39</v>
       </c>
       <c r="I25">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="J25" t="s">
         <v>15</v>
       </c>
       <c r="K25">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1125,16 +1155,16 @@
         <v>14</v>
       </c>
       <c r="H26">
-        <v>0.5600000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="I26">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="J26" t="s">
         <v>15</v>
       </c>
       <c r="K26">
-        <v>0.5600000000000001</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1154,7 +1184,7 @@
         <v>14</v>
       </c>
       <c r="H27">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="I27">
         <v>2</v>
@@ -1163,7 +1193,7 @@
         <v>15</v>
       </c>
       <c r="K27">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1183,16 +1213,16 @@
         <v>14</v>
       </c>
       <c r="H28">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
       <c r="I28">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
       </c>
       <c r="K28">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1212,16 +1242,16 @@
         <v>14</v>
       </c>
       <c r="H29">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="I29">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="J29" t="s">
         <v>15</v>
       </c>
       <c r="K29">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1241,16 +1271,16 @@
         <v>14</v>
       </c>
       <c r="H30">
-        <v>0.46</v>
+        <v>0.09</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
       </c>
       <c r="K30">
-        <v>0.46</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1270,16 +1300,16 @@
         <v>14</v>
       </c>
       <c r="H31">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="I31">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
       </c>
       <c r="K31">
-        <v>0.58</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1299,16 +1329,16 @@
         <v>14</v>
       </c>
       <c r="H32">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="I32">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="J32" t="s">
         <v>15</v>
       </c>
       <c r="K32">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1328,16 +1358,16 @@
         <v>14</v>
       </c>
       <c r="H33">
-        <v>0.57</v>
+        <v>0.26</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J33" t="s">
         <v>15</v>
       </c>
       <c r="K33">
-        <v>0.57</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1357,16 +1387,16 @@
         <v>14</v>
       </c>
       <c r="H34">
-        <v>0.5600000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="I34">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J34" t="s">
         <v>15</v>
       </c>
       <c r="K34">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1386,16 +1416,16 @@
         <v>14</v>
       </c>
       <c r="H35">
-        <v>0.62</v>
+        <v>0.51</v>
       </c>
       <c r="I35">
-        <v>153</v>
+        <v>64</v>
       </c>
       <c r="J35" t="s">
         <v>15</v>
       </c>
       <c r="K35">
-        <v>0.61</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1415,16 +1445,16 @@
         <v>14</v>
       </c>
       <c r="H36">
-        <v>0.49</v>
+        <v>0.25</v>
       </c>
       <c r="I36">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J36" t="s">
         <v>15</v>
       </c>
       <c r="K36">
-        <v>0.48</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1444,16 +1474,16 @@
         <v>14</v>
       </c>
       <c r="H37">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
       <c r="I37">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J37" t="s">
         <v>15</v>
       </c>
       <c r="K37">
-        <v>0.5600000000000001</v>
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
